--- a/rtos-api-analysis/results/threadx-6.4.2_runtime_info.xlsx
+++ b/rtos-api-analysis/results/threadx-6.4.2_runtime_info.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: /home/klee/klee_src/test-rtos/threadx-6.4.2//common/src/tx_thread_system_resume.c:196
+          <t xml:space="preserve">KLEE: Execute: /home/klee/klee_src/test-rtos/threadx-6.4.2//common/src/tx_queue_front_send.c:245
 </t>
         </is>
       </c>
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -676,16 +676,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41930</t>
+          <t>41738</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -955,36 +955,37 @@
           <t>byte_release</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B14" t="n">
+        <v>387</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>104466</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: /home/klee/klee_src/test-rtos/threadx-6.4.2//ports_module/cortex_m33/gnu/inc/tx_port.h:670
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -995,7 +996,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1035,7 +1036,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1115,7 +1116,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1195,7 +1196,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1275,7 +1276,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1315,7 +1316,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1355,7 +1356,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1395,7 +1396,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1475,7 +1476,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1542,290 +1543,290 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t xml:space="preserve">KLEE: Execute: /home/klee/klee_src/test-rtos/threadx-6.4.2//common/src/tx_queue_send.c:234
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>timer_create</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>104</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>25233</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>thread_create</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>233</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>byte_pool_performance_system_info_get</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>event_flags_performance_info_get</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2296</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>timer_change</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1278</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>module_callback_request_thread_entry</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>mutex_put</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t xml:space="preserve">KLEE: Execute: /home/klee/klee_src/test-rtos/threadx-6.4.2//ports_module/cortex_m33/gnu/inc/tx_port.h:673
 </t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>timer_create</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>31</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>25233</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>thread_create</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>66</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>byte_pool_performance_system_info_get</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>event_flags_performance_info_get</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>timer_change</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1278</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>module_callback_request_thread_entry</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>mutex_put</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KLEE: Execute: /home/klee/klee_src/test-rtos/threadx-6.4.2//common/src/tx_thread_system_resume.c:416
-</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -1873,7 +1874,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1913,7 +1914,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1953,26 +1954,26 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>776</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>50666</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2073,7 +2074,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2113,7 +2114,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2193,7 +2194,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2233,7 +2234,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2313,7 +2314,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2353,21 +2354,21 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2393,7 +2394,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2433,7 +2434,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2473,7 +2474,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2513,7 +2514,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2553,7 +2554,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2593,7 +2594,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2673,7 +2674,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2712,36 +2713,37 @@
           <t>queue_receive</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B58" t="n">
+        <v>633</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>4460</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>166798</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: /home/klee/klee_src/test-rtos/threadx-6.4.2//common/src/tx_thread_system_resume.c:391
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2752,16 +2754,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52</v>
+        <v>194</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>42742</t>
+          <t>42502</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2771,12 +2773,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2832,7 +2834,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2872,7 +2874,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2912,7 +2914,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2952,21 +2954,21 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2992,7 +2994,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3032,7 +3034,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3072,7 +3074,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3112,7 +3114,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3152,21 +3154,21 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>70</v>
+        <v>228</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>76715</t>
+          <t>68537</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3192,7 +3194,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3232,7 +3234,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3272,7 +3274,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3312,7 +3314,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3392,7 +3394,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3431,36 +3433,37 @@
           <t>block_release</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B76" t="n">
+        <v>0</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: /home/klee/klee_src/test-rtos/threadx-6.4.2//common/src/tx_block_release.c:190
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3514,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3551,21 +3554,21 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3671,21 +3674,21 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>280</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>280</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3711,7 +3714,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3751,7 +3754,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>85</v>
+        <v>281</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3791,7 +3794,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3831,7 +3834,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3871,7 +3874,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -3911,7 +3914,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3951,7 +3954,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -3990,36 +3993,37 @@
           <t>event_flags_set</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B90" t="n">
+        <v>832</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>5299</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>198336</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: /home/klee/klee_src/test-rtos/threadx-6.4.2//common/src/tx_thread_system_resume.c:525
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4034,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4070,7 +4074,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4150,7 +4154,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4190,7 +4194,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4270,7 +4274,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4310,7 +4314,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.96875</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
